--- a/cet4/result/58_侦探女神_商业真相追踪者/58_侦探女神_商业真相追踪者_学习版.xlsx
+++ b/cet4/result/58_侦探女神_商业真相追踪者/58_侦探女神_商业真相追踪者_学习版.xlsx
@@ -397,815 +397,717 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D50"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>sunset</v>
       </c>
       <c r="B2" t="str">
-        <v>sunset</v>
+        <v>/ˈsʌnset/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>日落</v>
       </c>
-      <c r="D2" t="str">
-        <v>sunset(日落)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>hat</v>
       </c>
       <c r="B3" t="str">
-        <v>hat</v>
+        <v>/hæt/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>帽子</v>
       </c>
-      <c r="D3" t="str">
-        <v>hat(帽子)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>atomic</v>
       </c>
       <c r="B4" t="str">
-        <v>atomic</v>
+        <v>/əˈtɑːmɪk/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>原子</v>
       </c>
-      <c r="D4" t="str">
-        <v>atomic(原子)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>customer</v>
       </c>
       <c r="B5" t="str">
-        <v>customer</v>
+        <v>/ˈkʌstəmər/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>顾客</v>
       </c>
-      <c r="D5" t="str">
-        <v>customer(顾客)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>tribe</v>
       </c>
       <c r="B6" t="str">
-        <v>tribe</v>
+        <v>/traɪb/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>集团</v>
       </c>
-      <c r="D6" t="str">
-        <v>tribe(集团)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>vacant</v>
       </c>
       <c r="B7" t="str">
-        <v>vacant</v>
+        <v>/ˈveɪkənt/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>空缺的</v>
       </c>
-      <c r="D7" t="str">
-        <v>vacant(空缺的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>file</v>
       </c>
       <c r="B8" t="str">
-        <v>file</v>
+        <v>/faɪl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>文件</v>
       </c>
-      <c r="D8" t="str">
-        <v>file(文件)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>overnight</v>
       </c>
       <c r="B9" t="str">
-        <v>overnight</v>
+        <v>/ˌoʊvərˈnaɪt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D9" t="str">
         <v>一夜之间</v>
       </c>
-      <c r="D9" t="str">
-        <v>overnight(一夜之间)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>normally</v>
       </c>
       <c r="B10" t="str">
-        <v>normally</v>
+        <v>/ˈnɔːrməli/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>通常</v>
       </c>
-      <c r="D10" t="str">
-        <v>normally(通常)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>steal</v>
       </c>
       <c r="B11" t="str">
-        <v>steal</v>
+        <v>/stiːl/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>偷窃</v>
       </c>
-      <c r="D11" t="str">
-        <v>steal(偷窃)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>sense</v>
       </c>
       <c r="B12" t="str">
-        <v>sense</v>
+        <v>/sens/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>感觉</v>
       </c>
-      <c r="D12" t="str">
-        <v>sense(感觉)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>stadium</v>
       </c>
       <c r="B13" t="str">
-        <v>stadium</v>
+        <v>/ˈsteɪdiəm/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>体育场</v>
       </c>
-      <c r="D13" t="str">
-        <v>stadium(体育场)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>zebra</v>
       </c>
       <c r="B14" t="str">
-        <v>zebra</v>
+        <v>/ˈziːbrə/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>斑马</v>
       </c>
-      <c r="D14" t="str">
-        <v>zebra(斑马)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>smooth</v>
       </c>
       <c r="B15" t="str">
-        <v>smooth</v>
+        <v>/smuːð/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D15" t="str">
         <v>圆滑的</v>
       </c>
-      <c r="D15" t="str">
-        <v>smooth(圆滑的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>superior</v>
       </c>
       <c r="B16" t="str">
-        <v>superior</v>
+        <v>/suːˈpɪriər/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>傲慢的</v>
       </c>
-      <c r="D16" t="str">
-        <v>superior(傲慢的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>elementary</v>
       </c>
       <c r="B17" t="str">
-        <v>elementary</v>
+        <v>/ˌelɪˈmentri/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>基本的</v>
       </c>
-      <c r="D17" t="str">
-        <v>elementary(基本的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>explain</v>
       </c>
       <c r="B18" t="str">
-        <v>explain</v>
+        <v>/ɪkˈspleɪn/</v>
       </c>
       <c r="C18" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D18" t="str">
         <v>解释</v>
       </c>
-      <c r="D18" t="str">
-        <v>explain(解释)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>acquaintance</v>
       </c>
       <c r="B19" t="str">
-        <v>acquaintance</v>
+        <v>/əˈkweɪntəns/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>熟人</v>
       </c>
-      <c r="D19" t="str">
-        <v>acquaintance(熟人)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>ski</v>
       </c>
       <c r="B20" t="str">
-        <v>ski</v>
+        <v>/skiː/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./vi./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>滑雪</v>
       </c>
-      <c r="D20" t="str">
-        <v>ski(滑雪)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>playground</v>
       </c>
       <c r="B21" t="str">
-        <v>playground</v>
+        <v>/ˈpleɪɡraʊnd/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>游乐场</v>
       </c>
-      <c r="D21" t="str">
-        <v>playground(游乐场)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>shy</v>
       </c>
       <c r="B22" t="str">
-        <v>shy</v>
+        <v>/ʃaɪ/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>害羞的</v>
       </c>
-      <c r="D22" t="str">
-        <v>shy(害羞的)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>manufacture</v>
       </c>
       <c r="B23" t="str">
-        <v>manufacture</v>
+        <v>/ˌmænjuˈfæktʃər/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D23" t="str">
         <v>制造</v>
       </c>
-      <c r="D23" t="str">
-        <v>manufacture(制造)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>mystery</v>
       </c>
       <c r="B24" t="str">
-        <v>mystery</v>
+        <v>/ˈmɪstəri/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>谜团</v>
       </c>
-      <c r="D24" t="str">
-        <v>mystery(谜团)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>attach</v>
       </c>
       <c r="B25" t="str">
-        <v>attach</v>
+        <v>/əˈtætʃ/</v>
       </c>
       <c r="C25" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D25" t="str">
         <v>附着</v>
       </c>
-      <c r="D25" t="str">
-        <v>attach(附着)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>radar</v>
       </c>
       <c r="B26" t="str">
-        <v>radar</v>
+        <v>/ˈreɪdɑːr/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>雷达</v>
       </c>
-      <c r="D26" t="str">
-        <v>radar(雷达)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>plate</v>
       </c>
       <c r="B27" t="str">
-        <v>plate</v>
+        <v>/pleɪt/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D27" t="str">
         <v>金属牌</v>
       </c>
-      <c r="D27" t="str">
-        <v>plate(金属牌)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>injection</v>
       </c>
       <c r="B28" t="str">
-        <v>injection</v>
+        <v>/ɪnˈdʒekʃn/</v>
       </c>
       <c r="C28" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>注射</v>
       </c>
-      <c r="D28" t="str">
-        <v>injection(注射)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>phenomenon</v>
       </c>
       <c r="B29" t="str">
-        <v>phenomenon</v>
+        <v>/fəˈnɑːmɪnən/</v>
       </c>
       <c r="C29" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>现象</v>
       </c>
-      <c r="D29" t="str">
-        <v>phenomenon(现象)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>extent</v>
       </c>
       <c r="B30" t="str">
-        <v>extent</v>
+        <v>/ɪkˈstent/</v>
       </c>
       <c r="C30" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>程度</v>
       </c>
-      <c r="D30" t="str">
-        <v>extent(程度)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>threat</v>
       </c>
       <c r="B31" t="str">
-        <v>threat</v>
+        <v>/θret/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>威胁</v>
       </c>
-      <c r="D31" t="str">
-        <v>threat(威胁)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>automation</v>
       </c>
       <c r="B32" t="str">
-        <v>superior</v>
+        <v>/ˌɔːtəˈmeɪʃn/</v>
       </c>
       <c r="C32" t="str">
-        <v>上级</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>superior(上级)📢</v>
+        <v>自动化</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>torture</v>
       </c>
       <c r="B33" t="str">
-        <v>automation</v>
+        <v>/ˈtɔːrtʃər/</v>
       </c>
       <c r="C33" t="str">
-        <v>自动化</v>
+        <v>n./v.</v>
       </c>
       <c r="D33" t="str">
-        <v>automation(自动化)📢</v>
+        <v>折磨</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>idea</v>
       </c>
       <c r="B34" t="str">
-        <v>torture</v>
+        <v>/aɪˈdiːə/</v>
       </c>
       <c r="C34" t="str">
-        <v>折磨</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>torture(折磨)📢</v>
+        <v>想法</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>service</v>
       </c>
       <c r="B35" t="str">
-        <v>idea</v>
+        <v>/ˈsɜːrvɪs/</v>
       </c>
       <c r="C35" t="str">
-        <v>想法</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>idea(想法)📢</v>
+        <v>服务</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>gracious</v>
       </c>
       <c r="B36" t="str">
-        <v>service</v>
+        <v>/ˈɡreɪʃəs/</v>
       </c>
       <c r="C36" t="str">
-        <v>服务</v>
+        <v>adj./int.</v>
       </c>
       <c r="D36" t="str">
-        <v>service(服务)📢</v>
+        <v>亲切的</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>philosophy</v>
       </c>
       <c r="B37" t="str">
-        <v>gracious</v>
+        <v>/fəˈlɑːsəfi/</v>
       </c>
       <c r="C37" t="str">
-        <v>亲切的</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>gracious(亲切的)📢</v>
+        <v>哲学</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>twist</v>
       </c>
       <c r="B38" t="str">
-        <v>philosophy</v>
+        <v>/twɪst/</v>
       </c>
       <c r="C38" t="str">
-        <v>哲学</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>philosophy(哲学)📢</v>
+        <v>扭动</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>surprising</v>
       </c>
       <c r="B39" t="str">
-        <v>twist</v>
+        <v>/sərˈpraɪzɪŋ/</v>
       </c>
       <c r="C39" t="str">
-        <v>扭动</v>
+        <v>v./adj.</v>
       </c>
       <c r="D39" t="str">
-        <v>twist(扭动)📢</v>
+        <v>令人惊讶的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>illegal</v>
       </c>
       <c r="B40" t="str">
-        <v>surprising</v>
+        <v>/ɪˈliːɡl/</v>
       </c>
       <c r="C40" t="str">
-        <v>令人惊讶的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D40" t="str">
-        <v>surprising(令人惊讶的)📢</v>
+        <v>非法的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>date</v>
       </c>
       <c r="B41" t="str">
-        <v>illegal</v>
+        <v>/deɪt/</v>
       </c>
       <c r="C41" t="str">
-        <v>非法的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D41" t="str">
-        <v>illegal(非法的)📢</v>
+        <v>日期</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>arrest</v>
       </c>
       <c r="B42" t="str">
-        <v>playground</v>
+        <v>/əˈrest/</v>
       </c>
       <c r="C42" t="str">
-        <v>游乐场</v>
+        <v>n./v.</v>
       </c>
       <c r="D42" t="str">
-        <v>playground(游乐场)📢</v>
+        <v>逮捕</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>story</v>
       </c>
       <c r="B43" t="str">
-        <v>date</v>
+        <v>/ˈstɔːri/</v>
       </c>
       <c r="C43" t="str">
-        <v>日期</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>date(日期)📢</v>
+        <v>故事</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>capacity</v>
       </c>
       <c r="B44" t="str">
-        <v>arrest</v>
+        <v>/kəˈpæsəti/</v>
       </c>
       <c r="C44" t="str">
-        <v>逮捕</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>arrest(逮捕)📢</v>
+        <v>能力</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>expose</v>
       </c>
       <c r="B45" t="str">
-        <v>story</v>
+        <v>/ɪkˈspoʊz/</v>
       </c>
       <c r="C45" t="str">
-        <v>故事</v>
+        <v>vt.</v>
       </c>
       <c r="D45" t="str">
-        <v>story(故事)📢</v>
+        <v>曝光</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>ready</v>
       </c>
       <c r="B46" t="str">
-        <v>stadium</v>
+        <v>/ˈredi/</v>
       </c>
       <c r="C46" t="str">
-        <v>体育馆</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D46" t="str">
-        <v>stadium(体育馆)📢</v>
+        <v>准备好</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>resolution</v>
       </c>
       <c r="B47" t="str">
-        <v>shy</v>
+        <v>/ˌrezəˈluːʃn/</v>
       </c>
       <c r="C47" t="str">
-        <v>羞涩</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>shy(羞涩)📢</v>
+        <v>决议</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>trumpet</v>
       </c>
       <c r="B48" t="str">
-        <v>capacity</v>
+        <v>/ˈtrʌmpɪt/</v>
       </c>
       <c r="C48" t="str">
-        <v>能力</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>capacity(能力)📢</v>
+        <v>喇叭</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>write</v>
       </c>
       <c r="B49" t="str">
-        <v>manufacture</v>
+        <v>/raɪt/</v>
       </c>
       <c r="C49" t="str">
-        <v>制造</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D49" t="str">
-        <v>manufacture(制造)📢</v>
+        <v>写</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>jealous</v>
       </c>
       <c r="B50" t="str">
-        <v>expose</v>
+        <v>/ˈdʒeləs/</v>
       </c>
       <c r="C50" t="str">
-        <v>曝光</v>
+        <v>adj.</v>
       </c>
       <c r="D50" t="str">
-        <v>expose(曝光)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>ready</v>
-      </c>
-      <c r="C51" t="str">
-        <v>准备好</v>
-      </c>
-      <c r="D51" t="str">
-        <v>ready(准备好)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>hat</v>
-      </c>
-      <c r="C52" t="str">
-        <v>帽子</v>
-      </c>
-      <c r="D52" t="str">
-        <v>hat(帽子)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>sunset</v>
-      </c>
-      <c r="C53" t="str">
-        <v>日落</v>
-      </c>
-      <c r="D53" t="str">
-        <v>sunset(日落)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>resolution</v>
-      </c>
-      <c r="C54" t="str">
-        <v>决议</v>
-      </c>
-      <c r="D54" t="str">
-        <v>resolution(决议)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>trumpet</v>
-      </c>
-      <c r="C55" t="str">
-        <v>喇叭</v>
-      </c>
-      <c r="D55" t="str">
-        <v>trumpet(喇叭)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>write</v>
-      </c>
-      <c r="C56" t="str">
-        <v>写</v>
-      </c>
-      <c r="D56" t="str">
-        <v>write(写)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>jealous</v>
-      </c>
-      <c r="C57" t="str">
         <v>审慎的</v>
-      </c>
-      <c r="D57" t="str">
-        <v>jealous(审慎的)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D50"/>
   </ignoredErrors>
 </worksheet>
 </file>